--- a/data/data/MAI391/MAI391_FA25_FE.xlsx
+++ b/data/data/MAI391/MAI391_FA25_FE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Documents\Personal project\luyenDe\data\data\MAI391\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FF41676-7594-41ED-8199-072006555045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{414AEF99-0C70-40B5-91A5-AA2FDC943DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12646" xr2:uid="{C0C34996-E748-42C4-95A2-2B57E6F91B9D}"/>
   </bookViews>
@@ -38,9 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="46">
   <si>
-    <t>question_id</t>
-  </si>
-  <si>
     <t>correct_answer</t>
   </si>
   <si>
@@ -174,6 +171,9 @@
   </si>
   <si>
     <t>https://fuoverflow.com/media/q40-webp.112427/full</t>
+  </si>
+  <si>
+    <t>link_media</t>
   </si>
 </sst>
 </file>
@@ -556,330 +556,330 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B34" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B35" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B37" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B38" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B39" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B41" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
